--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B.ROSER.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B.ROSER.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8319</v>
+        <v>26.7752</v>
       </c>
       <c r="E2" t="n">
-        <v>20.209</v>
+        <v>7.280900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6232</v>
+        <v>19.4944</v>
       </c>
       <c r="G2" t="n">
-        <v>9.208500000000001</v>
+        <v>26.4321</v>
       </c>
       <c r="H2" t="n">
-        <v>9.3653</v>
+        <v>19.6811</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1573999999999998</v>
+        <v>6.750700000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>22.6201</v>
+        <v>46.4931</v>
       </c>
       <c r="K2" t="n">
-        <v>18.6844</v>
+        <v>39.7383</v>
       </c>
       <c r="L2" t="n">
-        <v>3.936</v>
+        <v>6.754899999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-13.4116</v>
+        <v>-20.0609</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.318999999999999</v>
+        <v>-20.0566</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.0929</v>
+        <v>-0.004100000000000326</v>
       </c>
       <c r="P2" t="n">
-        <v>7.3403</v>
+        <v>-1.1902</v>
       </c>
       <c r="Q2" t="n">
-        <v>-21.0286</v>
+        <v>-49.0004</v>
       </c>
       <c r="R2" t="n">
-        <v>28.3693</v>
+        <v>47.8108</v>
       </c>
       <c r="S2" t="n">
-        <v>20.3723</v>
+        <v>-5.740699999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>17.981</v>
+        <v>-5.0594</v>
       </c>
       <c r="U2" t="n">
-        <v>2.391</v>
+        <v>-0.6813999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>-5.0891</v>
+        <v>7.274</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6364</v>
+        <v>14.8481</v>
       </c>
       <c r="X2" t="n">
-        <v>-5.7255</v>
+        <v>-7.5739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>19.2426</v>
+        <v>20.0767</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1985</v>
+        <v>8.555200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>8.044199999999998</v>
+        <v>11.5219</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.414300000000001</v>
+        <v>9.208500000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.5223</v>
+        <v>9.3653</v>
       </c>
       <c r="I3" t="n">
-        <v>2.108</v>
+        <v>-0.1573999999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>20.6472</v>
+        <v>22.6201</v>
       </c>
       <c r="K3" t="n">
-        <v>8.6561</v>
+        <v>18.6844</v>
       </c>
       <c r="L3" t="n">
-        <v>11.9911</v>
+        <v>3.936</v>
       </c>
       <c r="M3" t="n">
-        <v>-24.0614</v>
+        <v>-13.4116</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.1781</v>
+        <v>-9.318999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.883000000000001</v>
+        <v>-4.0929</v>
       </c>
       <c r="P3" t="n">
-        <v>11.3079</v>
+        <v>7.3403</v>
       </c>
       <c r="Q3" t="n">
-        <v>-29.7574</v>
+        <v>-21.0286</v>
       </c>
       <c r="R3" t="n">
-        <v>41.0658</v>
+        <v>28.3693</v>
       </c>
       <c r="S3" t="n">
-        <v>22.5245</v>
+        <v>8.6173</v>
       </c>
       <c r="T3" t="n">
-        <v>13.4647</v>
+        <v>6.3271</v>
       </c>
       <c r="U3" t="n">
-        <v>9.059900000000001</v>
+        <v>2.2899</v>
       </c>
       <c r="V3" t="n">
-        <v>-11.1756</v>
+        <v>-5.0891</v>
       </c>
       <c r="W3" t="n">
-        <v>6.8444</v>
+        <v>0.6364</v>
       </c>
       <c r="X3" t="n">
-        <v>-18.02</v>
+        <v>-5.7255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>12.9528</v>
+        <v>5.986800000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.217300000000002</v>
+        <v>1.692699999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>18.1706</v>
+        <v>4.294300000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>26.4321</v>
+        <v>-3.414300000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>19.6811</v>
+        <v>-5.5223</v>
       </c>
       <c r="I4" t="n">
-        <v>6.750700000000001</v>
+        <v>2.108</v>
       </c>
       <c r="J4" t="n">
-        <v>46.4931</v>
+        <v>20.6472</v>
       </c>
       <c r="K4" t="n">
-        <v>39.7383</v>
+        <v>8.6561</v>
       </c>
       <c r="L4" t="n">
-        <v>6.754899999999999</v>
+        <v>11.9911</v>
       </c>
       <c r="M4" t="n">
-        <v>-20.0609</v>
+        <v>-24.0614</v>
       </c>
       <c r="N4" t="n">
-        <v>-20.0566</v>
+        <v>-14.1781</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.004100000000000326</v>
+        <v>-9.883000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1902</v>
+        <v>11.3079</v>
       </c>
       <c r="Q4" t="n">
-        <v>-49.0004</v>
+        <v>-29.7574</v>
       </c>
       <c r="R4" t="n">
-        <v>47.8108</v>
+        <v>41.0658</v>
       </c>
       <c r="S4" t="n">
-        <v>-19.5627</v>
+        <v>9.268800000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-17.5576</v>
+        <v>3.9591</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.0055</v>
+        <v>5.3101</v>
       </c>
       <c r="V4" t="n">
-        <v>7.274</v>
+        <v>-11.1756</v>
       </c>
       <c r="W4" t="n">
-        <v>14.8481</v>
+        <v>6.8444</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.5739</v>
+        <v>-18.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6028</v>
+        <v>5.502000000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07830000000000004</v>
+        <v>3.787600000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6812</v>
+        <v>1.7145</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.066000000000001</v>
+        <v>21.149</v>
       </c>
       <c r="H5" t="n">
-        <v>13.1594</v>
+        <v>9.862500000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.2253</v>
+        <v>11.2865</v>
       </c>
       <c r="J5" t="n">
-        <v>21.9305</v>
+        <v>44.9271</v>
       </c>
       <c r="K5" t="n">
-        <v>27.4237</v>
+        <v>28.1946</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.4932</v>
+        <v>16.7322</v>
       </c>
       <c r="M5" t="n">
-        <v>-24.9965</v>
+        <v>-23.7779</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.2645</v>
+        <v>-18.3324</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.7322</v>
+        <v>-5.4458</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.372300000000001</v>
+        <v>-19.8385</v>
       </c>
       <c r="Q5" t="n">
-        <v>-35.7089</v>
+        <v>-63.6811</v>
       </c>
       <c r="R5" t="n">
-        <v>32.3367</v>
+        <v>43.8429</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3694999999999995</v>
+        <v>2.9548</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.5488</v>
+        <v>0.5127999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>2.9184</v>
+        <v>2.442</v>
       </c>
       <c r="V5" t="n">
-        <v>10.6717</v>
+        <v>1.2368</v>
       </c>
       <c r="W5" t="n">
-        <v>16.2491</v>
+        <v>22.0295</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.577199999999999</v>
+        <v>-20.7928</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>1.223100000000001</v>
+        <v>5.307499999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8888999999999996</v>
+        <v>1.3895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3346</v>
+        <v>3.9178</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.551699999999999</v>
+        <v>-3.066000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-12.2837</v>
+        <v>13.1594</v>
       </c>
       <c r="I6" t="n">
-        <v>7.732</v>
+        <v>-16.2253</v>
       </c>
       <c r="J6" t="n">
-        <v>10.8034</v>
+        <v>21.9305</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4445</v>
+        <v>27.4237</v>
       </c>
       <c r="L6" t="n">
-        <v>8.359</v>
+        <v>-5.4932</v>
       </c>
       <c r="M6" t="n">
-        <v>-15.355</v>
+        <v>-24.9965</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.7283</v>
+        <v>-14.2645</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6267</v>
+        <v>-10.7322</v>
       </c>
       <c r="P6" t="n">
-        <v>3.7693</v>
+        <v>-3.372300000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-25.1945</v>
+        <v>-35.7089</v>
       </c>
       <c r="R6" t="n">
-        <v>28.9645</v>
+        <v>32.3367</v>
       </c>
       <c r="S6" t="n">
-        <v>6.361</v>
+        <v>1.0741</v>
       </c>
       <c r="T6" t="n">
-        <v>6.9968</v>
+        <v>-1.0808</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6356000000000001</v>
+        <v>2.1548</v>
       </c>
       <c r="V6" t="n">
-        <v>-4.3555</v>
+        <v>10.6717</v>
       </c>
       <c r="W6" t="n">
-        <v>8.2837</v>
+        <v>16.2491</v>
       </c>
       <c r="X6" t="n">
-        <v>-12.639</v>
+        <v>-5.577199999999999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4072999999999993</v>
+        <v>3.7493</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.2693</v>
+        <v>-3.965100000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>7.6768</v>
+        <v>7.714199999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-11.1156</v>
@@ -1000,13 +1000,13 @@
         <v>24.5998</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8539000000000001</v>
+        <v>2.4882</v>
       </c>
       <c r="T7" t="n">
-        <v>-4.4026</v>
+        <v>-1.0982</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5488</v>
+        <v>3.5865</v>
       </c>
       <c r="V7" t="n">
         <v>8.4091</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>X. ASSALIT GARCÍA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2961999999999989</v>
+        <v>-4.394499999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.741599999999999</v>
+        <v>-1.627</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0375</v>
+        <v>-2.7674</v>
       </c>
       <c r="G8" t="n">
-        <v>21.149</v>
+        <v>-2.4255</v>
       </c>
       <c r="H8" t="n">
-        <v>9.862500000000001</v>
+        <v>0.3829999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>11.2865</v>
+        <v>-2.8085</v>
       </c>
       <c r="J8" t="n">
-        <v>44.9271</v>
+        <v>11.0765</v>
       </c>
       <c r="K8" t="n">
-        <v>28.1946</v>
+        <v>7.1423</v>
       </c>
       <c r="L8" t="n">
-        <v>16.7322</v>
+        <v>3.9341</v>
       </c>
       <c r="M8" t="n">
-        <v>-23.7779</v>
+        <v>-13.502</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.3324</v>
+        <v>-6.7594</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.4458</v>
+        <v>-6.7423</v>
       </c>
       <c r="P8" t="n">
-        <v>-19.8385</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q8" t="n">
-        <v>-63.6811</v>
+        <v>-21.0286</v>
       </c>
       <c r="R8" t="n">
-        <v>43.8429</v>
+        <v>19.0449</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.8433</v>
+        <v>-2.7166</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5334</v>
+        <v>-2.0339</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3098</v>
+        <v>-0.6823</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2368</v>
+        <v>2.7311</v>
       </c>
       <c r="W8" t="n">
-        <v>22.0295</v>
+        <v>10.3593</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.7928</v>
+        <v>-7.6281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. ASSALIT GARCÍA</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.936599999999999</v>
+        <v>-5.6806</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8198</v>
+        <v>-9.565800000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1166</v>
+        <v>3.8852</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4255</v>
+        <v>-18.2659</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3829999999999999</v>
+        <v>-11.5911</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8085</v>
+        <v>-6.6746</v>
       </c>
       <c r="J9" t="n">
-        <v>11.0765</v>
+        <v>-1.8784</v>
       </c>
       <c r="K9" t="n">
-        <v>7.1423</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>3.9341</v>
+        <v>-1.027499999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.502</v>
+        <v>-16.387</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.7594</v>
+        <v>-10.7399</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.7423</v>
+        <v>-5.6472</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9838</v>
+        <v>19.6401</v>
       </c>
       <c r="Q9" t="n">
-        <v>-21.0286</v>
+        <v>-11.5062</v>
       </c>
       <c r="R9" t="n">
-        <v>19.0449</v>
+        <v>31.1463</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.2583</v>
+        <v>-2.8227</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.2264</v>
+        <v>-2.6737</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.0316</v>
+        <v>-0.1484999999999998</v>
       </c>
       <c r="V9" t="n">
-        <v>2.7311</v>
+        <v>-4.2319</v>
       </c>
       <c r="W9" t="n">
-        <v>10.3593</v>
+        <v>6.4932</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.6281</v>
+        <v>-10.7251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.8149</v>
+        <v>-5.6923</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.7002</v>
+        <v>-6.8314</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8854</v>
+        <v>1.1395</v>
       </c>
       <c r="G10" t="n">
-        <v>-18.2659</v>
+        <v>-4.551699999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-11.5911</v>
+        <v>-12.2837</v>
       </c>
       <c r="I10" t="n">
-        <v>-6.6746</v>
+        <v>7.732</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8784</v>
+        <v>10.8034</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8512999999999999</v>
+        <v>2.4445</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.027499999999999</v>
+        <v>8.359</v>
       </c>
       <c r="M10" t="n">
-        <v>-16.387</v>
+        <v>-15.355</v>
       </c>
       <c r="N10" t="n">
-        <v>-10.7399</v>
+        <v>-14.7283</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.6472</v>
+        <v>-0.6267</v>
       </c>
       <c r="P10" t="n">
-        <v>19.6401</v>
+        <v>3.7693</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.5062</v>
+        <v>-25.1945</v>
       </c>
       <c r="R10" t="n">
-        <v>31.1463</v>
+        <v>28.9645</v>
       </c>
       <c r="S10" t="n">
-        <v>-6.956899999999999</v>
+        <v>-0.5539000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.808</v>
+        <v>-0.7235</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1487</v>
+        <v>0.1698</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.2319</v>
+        <v>-4.3555</v>
       </c>
       <c r="W10" t="n">
-        <v>6.4932</v>
+        <v>8.2837</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.7251</v>
+        <v>-12.639</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O. BAJJA SANCHEZ</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.3378</v>
+        <v>-9.703800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.8278</v>
+        <v>-20.5826</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5103</v>
+        <v>10.8788</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.4546</v>
+        <v>-19.5509</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.2829</v>
+        <v>-7.6192</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.172</v>
+        <v>-11.9316</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.5235</v>
+        <v>-11.2375</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.0451</v>
+        <v>1.5695</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4782</v>
+        <v>-12.8071</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.9313</v>
+        <v>-8.3134</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.2377</v>
+        <v>-9.1882</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.6935</v>
+        <v>0.8751</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1903</v>
+        <v>10.316</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.9514</v>
+        <v>-9.9191</v>
       </c>
       <c r="R11" t="n">
-        <v>7.141999999999999</v>
+        <v>20.2351</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9265000000000003</v>
+        <v>0.1617999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5357</v>
+        <v>-1.0928</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6091000000000001</v>
+        <v>1.2547</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.147</v>
+        <v>-0.6307</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.8170000000000001</v>
+        <v>1.6671</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.33</v>
+        <v>-2.2978</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>O. BAJJA SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.7156</v>
+        <v>-15.3504</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.9811</v>
+        <v>-13.3969</v>
       </c>
       <c r="F12" t="n">
-        <v>7.2655</v>
+        <v>-1.9535</v>
       </c>
       <c r="G12" t="n">
-        <v>-19.5509</v>
+        <v>-14.4546</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.6192</v>
+        <v>-7.2829</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.9316</v>
+        <v>-7.172</v>
       </c>
       <c r="J12" t="n">
-        <v>-11.2375</v>
+        <v>-5.5235</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5695</v>
+        <v>-4.0451</v>
       </c>
       <c r="L12" t="n">
-        <v>-12.8071</v>
+        <v>-1.4782</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.3134</v>
+        <v>-8.9313</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.1882</v>
+        <v>-3.2377</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8751</v>
+        <v>-5.6935</v>
       </c>
       <c r="P12" t="n">
-        <v>10.316</v>
+        <v>1.1903</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.9191</v>
+        <v>-5.9514</v>
       </c>
       <c r="R12" t="n">
-        <v>20.2351</v>
+        <v>7.141999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.8501</v>
+        <v>0.06110000000000015</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.4915</v>
+        <v>-1.105</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3584</v>
+        <v>1.1662</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6307</v>
+        <v>-2.147</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6671</v>
+        <v>-0.8170000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2978</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.445</v>
+        <v>-21.9237</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.782300000000001</v>
+        <v>-5.1418</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.6626</v>
+        <v>-16.7819</v>
       </c>
       <c r="G13" t="n">
         <v>-8.0722</v>
@@ -1468,13 +1468,13 @@
         <v>9.1258</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.4688</v>
+        <v>-2.9473</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7484</v>
+        <v>-2.108</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7203</v>
+        <v>-0.8395000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-13.8799</v>
@@ -1501,13 +1501,13 @@
         <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-34.4873</v>
+        <v>-27.801</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.1603</v>
+        <v>-15.4587</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.3271</v>
+        <v>-12.3421</v>
       </c>
       <c r="G14" t="n">
         <v>-11.7382</v>
@@ -1546,13 +1546,13 @@
         <v>20.0368</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.2754</v>
+        <v>-3.5891</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.3924</v>
+        <v>-2.691</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.8829</v>
+        <v>-0.898</v>
       </c>
       <c r="V14" t="n">
         <v>-15.6479</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-48.1547</v>
+        <v>-33.8367</v>
       </c>
       <c r="E15" t="n">
-        <v>-48.4271</v>
+        <v>-38.7907</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2721999999999998</v>
+        <v>4.9542</v>
       </c>
       <c r="G15" t="n">
         <v>-44.5453</v>
@@ -1624,13 +1624,13 @@
         <v>41.0656</v>
       </c>
       <c r="S15" t="n">
-        <v>-21.0188</v>
+        <v>-6.7009</v>
       </c>
       <c r="T15" t="n">
-        <v>-15.8911</v>
+        <v>-6.255</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.128</v>
+        <v>-0.4456999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>12.0531</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-85.92760000000001</v>
+        <v>-56.9855</v>
       </c>
       <c r="E16" t="n">
-        <v>-105.2255</v>
+        <v>-92.6541</v>
       </c>
       <c r="F16" t="n">
-        <v>19.2996</v>
+        <v>35.6699</v>
       </c>
       <c r="G16" t="n">
         <v>-84.41059999999999</v>
@@ -1678,10 +1678,10 @@
         <v>146.837</v>
       </c>
       <c r="K16" t="n">
-        <v>125.6073</v>
+        <v>125.6073000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>21.22950000000001</v>
+        <v>21.2295</v>
       </c>
       <c r="M16" t="n">
         <v>-231.2464</v>
@@ -1699,16 +1699,16 @@
         <v>-352.1292</v>
       </c>
       <c r="R16" t="n">
-        <v>394.7863000000001</v>
+        <v>394.7863</v>
       </c>
       <c r="S16" t="n">
-        <v>-29.3874</v>
+        <v>-0.4451000000000009</v>
       </c>
       <c r="T16" t="n">
-        <v>-27.6934</v>
+        <v>-15.1223</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.693599999999999</v>
+        <v>14.6786</v>
       </c>
       <c r="V16" t="n">
         <v>-14.7818</v>
